--- a/协作/模板/28-决策记录.xlsx
+++ b/协作/模板/28-决策记录.xlsx
@@ -2229,8 +2229,8 @@
     <dataValidation sqref="B2:B121" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="取值不合法" error="只能选择下拉里的值" type="list">
       <formula1>"技术,产品,流程,资源"</formula1>
     </dataValidation>
-    <dataValidation sqref="K2:K121" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="取值不合法" error="只能选择下拉里的值" type="list">
-      <formula1>"生效,已撤销"</formula1>
+    <dataValidation sqref="K2:K121" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"生效,已生效,已撤销"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
